--- a/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0001T0006Z000C1N28_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0001T0006Z000C1N28_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>3.617536633192392</v>
+        <v>0.5878497028937637</v>
       </c>
       <c r="D2" t="n">
-        <v>2.432814168303499</v>
+        <v>0.3953323023493187</v>
       </c>
       <c r="E2" t="n">
-        <v>4.083948505978164</v>
+        <v>0.6636416322214514</v>
       </c>
       <c r="F2" t="n">
-        <v>4.978815901324104</v>
+        <v>0.809057583965167</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>11.78543364514872</v>
+        <v>1.915132967336667</v>
       </c>
       <c r="D3" t="n">
-        <v>12.39044597095171</v>
+        <v>2.013447470279653</v>
       </c>
       <c r="E3" t="n">
-        <v>4.083948505978164</v>
+        <v>0.6636416322214514</v>
       </c>
       <c r="F3" t="n">
-        <v>4.978815901324104</v>
+        <v>0.809057583965167</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
